--- a/Timetable.xlsx
+++ b/Timetable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MAHESH\TSP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4060B3E-5C25-4D42-A0DB-FBDBEA70E259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36CC055-1928-45D6-AD0A-2C444CDB395F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{17065CC1-F5CA-4190-BC09-FC144115C7D8}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="31">
   <si>
     <t>MAHESH</t>
   </si>
@@ -127,6 +127,12 @@
   </si>
   <si>
     <t>Period</t>
+  </si>
+  <si>
+    <t>7A &amp; 7B</t>
+  </si>
+  <si>
+    <t>6A &amp; 6B</t>
   </si>
 </sst>
 </file>
@@ -722,8 +728,8 @@
       <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="2">
-        <v>7</v>
+      <c r="C12" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>9</v>
@@ -756,8 +762,8 @@
       <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="2">
-        <v>6</v>
+      <c r="C14" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>9</v>
